--- a/jogos_2024-11-07.xlsx
+++ b/jogos_2024-11-07.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>3.73</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.47</v>
       </c>
       <c r="N5" t="n">
-        <v>4.75</v>
+        <v>1.87</v>
       </c>
       <c r="O5" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>2.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.16</v>
+        <v>3.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58', '75']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45603.5</v>
@@ -1159,81 +1159,81 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Q6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.25</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.5</v>
+        <v>4.16</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AC6" t="n">
         <v>2.2</v>
@@ -1243,25 +1243,25 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['79', '90+5']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['14', '70', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45603.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.73</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.47</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X7" t="n">
         <v>2.55</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['79', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['14', '70', '88']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.38</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['58', '75']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45603.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,52 +1701,52 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>5.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2.1</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
         <v>1.36</v>
@@ -1759,25 +1759,25 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['2', '14', '19', '26', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.05</v>
+        <v>2.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.75</v>
+        <v>1.09</v>
       </c>
       <c r="AI10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>3.2</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45603.625</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,52 +1830,52 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N11" t="n">
         <v>5.5</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.6</v>
-      </c>
       <c r="O11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q11" t="n">
         <v>5.5</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.1</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
         <v>1.36</v>
@@ -1888,25 +1888,25 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['2', '14', '19', '26', '75']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['11']</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
-        <v>2.45</v>
+        <v>1.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.09</v>
+        <v>2.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45603.625</v>
